--- a/output/quarterly_fcst.xlsx
+++ b/output/quarterly_fcst.xlsx
@@ -445,82 +445,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>0.0208805925791523</v>
+        <v>0.039201355746544</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0124354923880415</v>
+        <v>0.00322028065927536</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0094285722137535</v>
+        <v>0.0162255563832863</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0137085970289119</v>
+        <v>0.0178842490994885</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0116535162493278</v>
+        <v>0.0188361010717453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0152291448571429</v>
+        <v>0.0138109476927603</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.00809513107510787</v>
+        <v>0.0051736264827301</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0110933048571429</v>
+        <v>0.0107359309493157</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.00905321</v>
+        <v>0.00821393807100047</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0114601855730138</v>
+        <v>0.0140162595148781</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0102811178584151</v>
+        <v>0.00832044263198439</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.00978740031042362</v>
+        <v>0.00628174906696502</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.00870214264866535</v>
+        <v>-0.0108618278166141</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0002270391583046</v>
+        <v>0.00244913370036726</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.014189029293438</v>
+        <v>0.02044411018464</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.00867489831384259</v>
+        <v>0.00467542944969886</v>
       </c>
     </row>
     <row r="17">
@@ -542,82 +542,82 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0157673092903483</v>
+        <v>0.0154386076172396</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0346048321271051</v>
+        <v>0.013659691874553</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0212922964955234</v>
+        <v>0.0147210562606515</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0227775548450109</v>
+        <v>0.0187902053728565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.010700609808618</v>
+        <v>0.0169553627125188</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.00981375329497534</v>
+        <v>0.017702015361575</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.000201914806921973</v>
+        <v>0.0177996761006313</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0134899483812819</v>
+        <v>0.011582472105742</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.00410226540317616</v>
+        <v>0.00778810895998739</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0068211392339032</v>
+        <v>0.0147857088629789</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0123808427045609</v>
+        <v>0.0132743582876122</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.0552564518828218</v>
+        <v>-0.00309077541782634</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0425850395894901</v>
+        <v>0.0108434905333412</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.00389125483007713</v>
+        <v>0.010683368843575</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.00052250343620875</v>
+        <v>0.00855271355228642</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.00861061688263711</v>
+        <v>0.0171450667313933</v>
       </c>
     </row>
   </sheetData>
@@ -636,82 +636,82 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.00533217771675943</v>
+        <v>0.0117326209820302</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0396539622290263</v>
+        <v>0.0108960504825199</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0120737130768321</v>
+        <v>0.0161802896959579</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0269607840701745</v>
+        <v>0.018865813994737</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.00705700553244672</v>
+        <v>0.0194895834451105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0108504453118194</v>
+        <v>0.0181146635128779</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.00176780822136012</v>
+        <v>0.0171766330360351</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0116711966390539</v>
+        <v>0.0141973969864204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.00583168398945792</v>
+        <v>0.00865166573210851</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.00624105290846388</v>
+        <v>0.0141642234284751</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.00523310503793818</v>
+        <v>0.015211729534928</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.0556701547941667</v>
+        <v>-0.00936389661164536</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0411255903442551</v>
+        <v>0.00943938906387804</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.00133733604531149</v>
+        <v>0.0106183406935087</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0128701211395183</v>
+        <v>0.00768883773290075</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.00533196143479599</v>
+        <v>0.0127475748282161</v>
       </c>
     </row>
   </sheetData>
@@ -730,82 +730,82 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0176754095457005</v>
+        <v>0.00224425051409125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0196025185899573</v>
+        <v>0.0118035666760139</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0195983324827831</v>
+        <v>0.0133111145982076</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0089881763643626</v>
+        <v>0.0115094421321763</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.00497620402692445</v>
+        <v>0.00210185036912208</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0108796365872164</v>
+        <v>0.0157817199394054</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.00756095389863892</v>
+        <v>0.0160173225725187</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.00892428904108794</v>
+        <v>0.00649367828427385</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.00280184425762874</v>
+        <v>-0.00656147880518532</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.00690130193258078</v>
+        <v>0.0120540133077287</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.00818965452454225</v>
+        <v>0.0139675151322535</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.00491417880802336</v>
+        <v>-0.00163609476351289</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0272884110375443</v>
+        <v>0.00368925767125473</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.0108515509893779</v>
+        <v>0.00990661223353952</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.00871304508941177</v>
+        <v>0.0129939038329548</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.0105652226220984</v>
+        <v>0.0091358992610698</v>
       </c>
     </row>
   </sheetData>
@@ -916,89 +916,55 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="n">
-        <v>0.025544147</v>
-      </c>
+      <c r="A1"/>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0.004977321</v>
-      </c>
+      <c r="A2"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>0.034455879</v>
-      </c>
+      <c r="A3"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>0.019256629</v>
-      </c>
+      <c r="A4"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>0.043838884</v>
-      </c>
+      <c r="A5"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>-0.006192574</v>
-      </c>
+      <c r="A6"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>0.014888004</v>
-      </c>
+      <c r="A7"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>0.000689339</v>
-      </c>
+      <c r="A8"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>0.018178553</v>
-      </c>
+      <c r="A9"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>0.009645883</v>
-      </c>
+      <c r="A10"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>0.006469049</v>
-      </c>
+      <c r="A11"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>-0.000479933</v>
-      </c>
+      <c r="A12"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>-0.059170532</v>
-      </c>
+      <c r="A13"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>0.039027404</v>
-      </c>
+      <c r="A14"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>-0.000780012</v>
-      </c>
+      <c r="A15"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>0.012234834</v>
-      </c>
+      <c r="A16"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>0.005069302</v>
-      </c>
+      <c r="A17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
